--- a/New_CenterOfRotation/Finite_COR/Data Files/C45_Data/Model 3 Y_Z Data.xlsx
+++ b/New_CenterOfRotation/Finite_COR/Data Files/C45_Data/Model 3 Y_Z Data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="23">
   <si>
     <t>Node 25454</t>
   </si>
@@ -75,13 +75,19 @@
     <t>Middle Back Top of C5</t>
   </si>
   <si>
-    <t/>
+    <t>Node</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Node </t>
   </si>
   <si>
     <t>Initial Coord.</t>
   </si>
   <si>
     <t>X (U1)</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -174,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -224,10 +230,10 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" quotePrefix="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" quotePrefix="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
@@ -244,6 +250,12 @@
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3515,8 +3527,8 @@
       <c r="AC2" s="15"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="17" t="s">
-        <v>18</v>
+      <c r="A3" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="B3" s="9">
         <v>25454</v>
@@ -3524,8 +3536,8 @@
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="6"/>
-      <c r="F3" s="17" t="s">
-        <v>18</v>
+      <c r="F3" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="G3" s="9">
         <v>31067</v>
@@ -3533,8 +3545,8 @@
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
       <c r="J3" s="6"/>
-      <c r="K3" s="17" t="s">
-        <v>18</v>
+      <c r="K3" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="L3" s="4">
         <v>29005</v>
@@ -3542,8 +3554,8 @@
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
       <c r="O3" s="6"/>
-      <c r="P3" s="17" t="s">
-        <v>18</v>
+      <c r="P3" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="Q3" s="4">
         <v>45615</v>
@@ -3551,8 +3563,8 @@
       <c r="R3" s="5"/>
       <c r="S3" s="5"/>
       <c r="T3" s="6"/>
-      <c r="U3" s="17" t="s">
-        <v>18</v>
+      <c r="U3" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V3" s="4">
         <v>52027</v>
@@ -3560,8 +3572,8 @@
       <c r="W3" s="5"/>
       <c r="X3" s="5"/>
       <c r="Y3" s="6"/>
-      <c r="Z3" s="18" t="s">
-        <v>18</v>
+      <c r="Z3" s="25" t="s">
+        <v>22</v>
       </c>
       <c r="AA3" s="19">
         <v>49903</v>
@@ -3571,7 +3583,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" s="10">
         <v>-6.65384</v>
@@ -3584,7 +3596,7 @@
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4" s="10">
         <v>6.11839</v>
@@ -3597,7 +3609,7 @@
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L4" s="5">
         <v>0.185553</v>
@@ -3610,7 +3622,7 @@
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q4" s="5">
         <v>-8.27627</v>
@@ -3623,7 +3635,7 @@
       </c>
       <c r="T4" s="6"/>
       <c r="U4" s="20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V4" s="5">
         <v>7.72579</v>
@@ -3636,7 +3648,7 @@
       </c>
       <c r="Y4" s="6"/>
       <c r="Z4" s="20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA4" s="22">
         <v>-0.0172085</v>
@@ -3653,7 +3665,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>7</v>
@@ -3666,7 +3678,7 @@
         <v>6</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>7</v>
@@ -3679,7 +3691,7 @@
         <v>6</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M5" s="8" t="s">
         <v>7</v>
@@ -3692,7 +3704,7 @@
         <v>6</v>
       </c>
       <c r="Q5" s="23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R5" s="8" t="s">
         <v>7</v>
@@ -3705,7 +3717,7 @@
         <v>6</v>
       </c>
       <c r="V5" s="23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W5" s="8" t="s">
         <v>7</v>
@@ -3718,7 +3730,7 @@
         <v>6</v>
       </c>
       <c r="AA5" s="23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB5" s="8" t="s">
         <v>7</v>
@@ -3731,7 +3743,7 @@
       <c r="A6" s="9">
         <v>0</v>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="26">
         <v>-0.267759</v>
       </c>
       <c r="C6" s="10">
@@ -3744,7 +3756,7 @@
       <c r="F6" s="9">
         <v>0</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="26">
         <v>-0.253219</v>
       </c>
       <c r="H6" s="10">
@@ -3770,7 +3782,7 @@
       <c r="P6" s="9">
         <v>0</v>
       </c>
-      <c r="Q6" s="24">
+      <c r="Q6" s="26">
         <v>-0.300879</v>
       </c>
       <c r="R6" s="10">
@@ -3783,7 +3795,7 @@
       <c r="U6" s="9">
         <v>0</v>
       </c>
-      <c r="V6" s="24">
+      <c r="V6" s="26">
         <v>-0.298353</v>
       </c>
       <c r="W6" s="10">
@@ -3796,7 +3808,7 @@
       <c r="Z6" s="9">
         <v>0</v>
       </c>
-      <c r="AA6" s="24">
+      <c r="AA6" s="26">
         <v>-0.29833</v>
       </c>
       <c r="AB6" s="10">
@@ -3810,7 +3822,7 @@
       <c r="A7" s="10">
         <v>0.05</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="26">
         <v>-0.167081</v>
       </c>
       <c r="C7" s="10">
@@ -3823,7 +3835,7 @@
       <c r="F7" s="10">
         <v>0.05</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="26">
         <v>-0.153077</v>
       </c>
       <c r="H7" s="10">
@@ -3849,7 +3861,7 @@
       <c r="P7" s="10">
         <v>0.05</v>
       </c>
-      <c r="Q7" s="24">
+      <c r="Q7" s="26">
         <v>-0.194766</v>
       </c>
       <c r="R7" s="10">
@@ -3862,7 +3874,7 @@
       <c r="U7" s="10">
         <v>0.05</v>
       </c>
-      <c r="V7" s="24">
+      <c r="V7" s="26">
         <v>-0.193563</v>
       </c>
       <c r="W7" s="10">
@@ -3875,7 +3887,7 @@
       <c r="Z7" s="10">
         <v>0.05</v>
       </c>
-      <c r="AA7" s="24">
+      <c r="AA7" s="26">
         <v>-0.202195</v>
       </c>
       <c r="AB7" s="10">
@@ -3889,7 +3901,7 @@
       <c r="A8" s="10">
         <v>0.1</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="26">
         <v>-0.211212</v>
       </c>
       <c r="C8" s="10">
@@ -3902,7 +3914,7 @@
       <c r="F8" s="10">
         <v>0.1</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="26">
         <v>-0.209975</v>
       </c>
       <c r="H8" s="10">
@@ -3928,7 +3940,7 @@
       <c r="P8" s="10">
         <v>0.1</v>
       </c>
-      <c r="Q8" s="24">
+      <c r="Q8" s="26">
         <v>-0.153682</v>
       </c>
       <c r="R8" s="10">
@@ -3941,7 +3953,7 @@
       <c r="U8" s="10">
         <v>0.1</v>
       </c>
-      <c r="V8" s="24">
+      <c r="V8" s="26">
         <v>-0.149815</v>
       </c>
       <c r="W8" s="10">
@@ -3954,7 +3966,7 @@
       <c r="Z8" s="10">
         <v>0.1</v>
       </c>
-      <c r="AA8" s="24">
+      <c r="AA8" s="26">
         <v>-0.1345</v>
       </c>
       <c r="AB8" s="10">
@@ -3968,7 +3980,7 @@
       <c r="A9" s="10">
         <v>0.15</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="26">
         <v>-0.37246</v>
       </c>
       <c r="C9" s="10">
@@ -3981,7 +3993,7 @@
       <c r="F9" s="10">
         <v>0.15</v>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="26">
         <v>-0.389987</v>
       </c>
       <c r="H9" s="10">
@@ -4007,7 +4019,7 @@
       <c r="P9" s="10">
         <v>0.15</v>
       </c>
-      <c r="Q9" s="24">
+      <c r="Q9" s="26">
         <v>-0.229667</v>
       </c>
       <c r="R9" s="10">
@@ -4020,7 +4032,7 @@
       <c r="U9" s="10">
         <v>0.15</v>
       </c>
-      <c r="V9" s="24">
+      <c r="V9" s="26">
         <v>-0.223371</v>
       </c>
       <c r="W9" s="10">
@@ -4033,7 +4045,7 @@
       <c r="Z9" s="10">
         <v>0.15</v>
       </c>
-      <c r="AA9" s="24">
+      <c r="AA9" s="26">
         <v>-0.169972</v>
       </c>
       <c r="AB9" s="10">
@@ -4047,7 +4059,7 @@
       <c r="A10" s="10">
         <v>0.2</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="26">
         <v>-0.639017</v>
       </c>
       <c r="C10" s="10">
@@ -4060,7 +4072,7 @@
       <c r="F10" s="10">
         <v>0.2</v>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="26">
         <v>-0.687174</v>
       </c>
       <c r="H10" s="10">
@@ -4086,7 +4098,7 @@
       <c r="P10" s="10">
         <v>0.2</v>
       </c>
-      <c r="Q10" s="24">
+      <c r="Q10" s="26">
         <v>-0.393943</v>
       </c>
       <c r="R10" s="10">
@@ -4099,7 +4111,7 @@
       <c r="U10" s="10">
         <v>0.2</v>
       </c>
-      <c r="V10" s="24">
+      <c r="V10" s="26">
         <v>-0.387658</v>
       </c>
       <c r="W10" s="10">
@@ -4112,7 +4124,7 @@
       <c r="Z10" s="10">
         <v>0.2</v>
       </c>
-      <c r="AA10" s="24">
+      <c r="AA10" s="26">
         <v>-0.281969</v>
       </c>
       <c r="AB10" s="10">
@@ -4126,7 +4138,7 @@
       <c r="A11" s="10">
         <v>0.25</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="26">
         <v>-0.77813</v>
       </c>
       <c r="C11" s="10">
@@ -4139,7 +4151,7 @@
       <c r="F11" s="10">
         <v>0.25</v>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="26">
         <v>-0.842584</v>
       </c>
       <c r="H11" s="10">
@@ -4165,7 +4177,7 @@
       <c r="P11" s="10">
         <v>0.25</v>
       </c>
-      <c r="Q11" s="24">
+      <c r="Q11" s="26">
         <v>-0.487316</v>
       </c>
       <c r="R11" s="10">
@@ -4178,7 +4190,7 @@
       <c r="U11" s="10">
         <v>0.25</v>
       </c>
-      <c r="V11" s="24">
+      <c r="V11" s="26">
         <v>-0.482244</v>
       </c>
       <c r="W11" s="10">
@@ -4191,7 +4203,7 @@
       <c r="Z11" s="10">
         <v>0.25</v>
       </c>
-      <c r="AA11" s="24">
+      <c r="AA11" s="26">
         <v>-0.352639</v>
       </c>
       <c r="AB11" s="10">
@@ -4205,7 +4217,7 @@
       <c r="A12" s="10">
         <v>0.30198</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="26">
         <v>-1.09566</v>
       </c>
       <c r="C12" s="10">
@@ -4218,7 +4230,7 @@
       <c r="F12" s="10">
         <v>0.30198</v>
       </c>
-      <c r="G12" s="24">
+      <c r="G12" s="26">
         <v>-1.19793</v>
       </c>
       <c r="H12" s="10">
@@ -4244,7 +4256,7 @@
       <c r="P12" s="10">
         <v>0.30198</v>
       </c>
-      <c r="Q12" s="24">
+      <c r="Q12" s="26">
         <v>-0.713313</v>
       </c>
       <c r="R12" s="10">
@@ -4257,7 +4269,7 @@
       <c r="U12" s="10">
         <v>0.30198</v>
       </c>
-      <c r="V12" s="24">
+      <c r="V12" s="26">
         <v>-0.713274</v>
       </c>
       <c r="W12" s="10">
@@ -4270,7 +4282,7 @@
       <c r="Z12" s="10">
         <v>0.30198</v>
       </c>
-      <c r="AA12" s="24">
+      <c r="AA12" s="26">
         <v>-0.533264</v>
       </c>
       <c r="AB12" s="10">
@@ -4284,7 +4296,7 @@
       <c r="A13" s="10">
         <v>0.35365</v>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="26">
         <v>-1.40013</v>
       </c>
       <c r="C13" s="10">
@@ -4297,7 +4309,7 @@
       <c r="F13" s="10">
         <v>0.35365</v>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="26">
         <v>-1.53959</v>
       </c>
       <c r="H13" s="10">
@@ -4323,7 +4335,7 @@
       <c r="P13" s="10">
         <v>0.35365</v>
       </c>
-      <c r="Q13" s="24">
+      <c r="Q13" s="26">
         <v>-0.941036</v>
       </c>
       <c r="R13" s="10">
@@ -4336,7 +4348,7 @@
       <c r="U13" s="10">
         <v>0.35365</v>
       </c>
-      <c r="V13" s="24">
+      <c r="V13" s="26">
         <v>-0.948458</v>
       </c>
       <c r="W13" s="10">
@@ -4349,7 +4361,7 @@
       <c r="Z13" s="10">
         <v>0.35365</v>
       </c>
-      <c r="AA13" s="24">
+      <c r="AA13" s="26">
         <v>-0.722679</v>
       </c>
       <c r="AB13" s="10">
@@ -4363,7 +4375,7 @@
       <c r="A14" s="10">
         <v>0.40358</v>
       </c>
-      <c r="B14" s="24">
+      <c r="B14" s="26">
         <v>-1.74036</v>
       </c>
       <c r="C14" s="10">
@@ -4376,7 +4388,7 @@
       <c r="F14" s="10">
         <v>0.40358</v>
       </c>
-      <c r="G14" s="24">
+      <c r="G14" s="26">
         <v>-1.92219</v>
       </c>
       <c r="H14" s="10">
@@ -4402,7 +4414,7 @@
       <c r="P14" s="10">
         <v>0.40358</v>
       </c>
-      <c r="Q14" s="24">
+      <c r="Q14" s="26">
         <v>-1.2028</v>
       </c>
       <c r="R14" s="10">
@@ -4415,7 +4427,7 @@
       <c r="U14" s="10">
         <v>0.40358</v>
       </c>
-      <c r="V14" s="24">
+      <c r="V14" s="26">
         <v>-1.22111</v>
       </c>
       <c r="W14" s="10">
@@ -4428,7 +4440,7 @@
       <c r="Z14" s="10">
         <v>0.40358</v>
       </c>
-      <c r="AA14" s="24">
+      <c r="AA14" s="26">
         <v>-0.946907</v>
       </c>
       <c r="AB14" s="10">
@@ -4442,7 +4454,7 @@
       <c r="A15" s="10">
         <v>0.45421</v>
       </c>
-      <c r="B15" s="24">
+      <c r="B15" s="26">
         <v>-2.06761</v>
       </c>
       <c r="C15" s="10">
@@ -4455,7 +4467,7 @@
       <c r="F15" s="10">
         <v>0.45421</v>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="26">
         <v>-2.29187</v>
       </c>
       <c r="H15" s="10">
@@ -4481,7 +4493,7 @@
       <c r="P15" s="10">
         <v>0.45421</v>
       </c>
-      <c r="Q15" s="24">
+      <c r="Q15" s="26">
         <v>-1.45887</v>
       </c>
       <c r="R15" s="10">
@@ -4494,7 +4506,7 @@
       <c r="U15" s="10">
         <v>0.45421</v>
       </c>
-      <c r="V15" s="24">
+      <c r="V15" s="26">
         <v>-1.49013</v>
       </c>
       <c r="W15" s="10">
@@ -4507,7 +4519,7 @@
       <c r="Z15" s="10">
         <v>0.45421</v>
       </c>
-      <c r="AA15" s="24">
+      <c r="AA15" s="26">
         <v>-1.17083</v>
       </c>
       <c r="AB15" s="10">
@@ -4521,7 +4533,7 @@
       <c r="A16" s="10">
         <v>0.50322</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="26">
         <v>-2.37488</v>
       </c>
       <c r="C16" s="10">
@@ -4534,7 +4546,7 @@
       <c r="F16" s="10">
         <v>0.50322</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="26">
         <v>-2.64075</v>
       </c>
       <c r="H16" s="10">
@@ -4560,7 +4572,7 @@
       <c r="P16" s="10">
         <v>0.50322</v>
       </c>
-      <c r="Q16" s="24">
+      <c r="Q16" s="26">
         <v>-1.70133</v>
       </c>
       <c r="R16" s="10">
@@ -4573,7 +4585,7 @@
       <c r="U16" s="10">
         <v>0.50322</v>
       </c>
-      <c r="V16" s="24">
+      <c r="V16" s="26">
         <v>-1.74684</v>
       </c>
       <c r="W16" s="10">
@@ -4586,7 +4598,7 @@
       <c r="Z16" s="10">
         <v>0.50322</v>
       </c>
-      <c r="AA16" s="24">
+      <c r="AA16" s="26">
         <v>-1.38618</v>
       </c>
       <c r="AB16" s="10">
@@ -4600,7 +4612,7 @@
       <c r="A17" s="10">
         <v>0.55384</v>
       </c>
-      <c r="B17" s="24">
+      <c r="B17" s="26">
         <v>-2.66904</v>
       </c>
       <c r="C17" s="10">
@@ -4613,7 +4625,7 @@
       <c r="F17" s="10">
         <v>0.55384</v>
       </c>
-      <c r="G17" s="24">
+      <c r="G17" s="26">
         <v>-2.97614</v>
       </c>
       <c r="H17" s="10">
@@ -4639,7 +4651,7 @@
       <c r="P17" s="10">
         <v>0.55384</v>
       </c>
-      <c r="Q17" s="24">
+      <c r="Q17" s="26">
         <v>-1.93563</v>
       </c>
       <c r="R17" s="10">
@@ -4652,7 +4664,7 @@
       <c r="U17" s="10">
         <v>0.55384</v>
       </c>
-      <c r="V17" s="24">
+      <c r="V17" s="26">
         <v>-1.99649</v>
       </c>
       <c r="W17" s="10">
@@ -4665,7 +4677,7 @@
       <c r="Z17" s="10">
         <v>0.55384</v>
       </c>
-      <c r="AA17" s="24">
+      <c r="AA17" s="26">
         <v>-1.59695</v>
       </c>
       <c r="AB17" s="10">
@@ -4679,7 +4691,7 @@
       <c r="A18" s="10">
         <v>0.60384</v>
       </c>
-      <c r="B18" s="24">
+      <c r="B18" s="26">
         <v>-3.00029</v>
       </c>
       <c r="C18" s="10">
@@ -4692,7 +4704,7 @@
       <c r="F18" s="10">
         <v>0.60384</v>
       </c>
-      <c r="G18" s="24">
+      <c r="G18" s="26">
         <v>-3.35691</v>
       </c>
       <c r="H18" s="10">
@@ -4718,7 +4730,7 @@
       <c r="P18" s="10">
         <v>0.60384</v>
       </c>
-      <c r="Q18" s="24">
+      <c r="Q18" s="26">
         <v>-2.20155</v>
       </c>
       <c r="R18" s="10">
@@ -4731,7 +4743,7 @@
       <c r="U18" s="10">
         <v>0.60384</v>
       </c>
-      <c r="V18" s="24">
+      <c r="V18" s="26">
         <v>-2.28222</v>
       </c>
       <c r="W18" s="10">
@@ -4744,7 +4756,7 @@
       <c r="Z18" s="10">
         <v>0.60384</v>
       </c>
-      <c r="AA18" s="24">
+      <c r="AA18" s="26">
         <v>-1.83681</v>
       </c>
       <c r="AB18" s="10">
@@ -4758,7 +4770,7 @@
       <c r="A19" s="10">
         <v>0.65565</v>
       </c>
-      <c r="B19" s="24">
+      <c r="B19" s="26">
         <v>-3.30951</v>
       </c>
       <c r="C19" s="10">
@@ -4771,7 +4783,7 @@
       <c r="F19" s="10">
         <v>0.65565</v>
       </c>
-      <c r="G19" s="24">
+      <c r="G19" s="26">
         <v>-3.71653</v>
       </c>
       <c r="H19" s="10">
@@ -4797,7 +4809,7 @@
       <c r="P19" s="10">
         <v>0.65565</v>
       </c>
-      <c r="Q19" s="24">
+      <c r="Q19" s="26">
         <v>-2.45063</v>
       </c>
       <c r="R19" s="10">
@@ -4810,7 +4822,7 @@
       <c r="U19" s="10">
         <v>0.65565</v>
       </c>
-      <c r="V19" s="24">
+      <c r="V19" s="26">
         <v>-2.55258</v>
       </c>
       <c r="W19" s="10">
@@ -4823,7 +4835,7 @@
       <c r="Z19" s="10">
         <v>0.65565</v>
       </c>
-      <c r="AA19" s="24">
+      <c r="AA19" s="26">
         <v>-2.06176</v>
       </c>
       <c r="AB19" s="10">
@@ -4837,7 +4849,7 @@
       <c r="A20" s="10">
         <v>0.70225</v>
       </c>
-      <c r="B20" s="24">
+      <c r="B20" s="26">
         <v>-3.71929</v>
       </c>
       <c r="C20" s="10">
@@ -4850,7 +4862,7 @@
       <c r="F20" s="10">
         <v>0.70225</v>
       </c>
-      <c r="G20" s="24">
+      <c r="G20" s="26">
         <v>-4.19734</v>
       </c>
       <c r="H20" s="10">
@@ -4876,7 +4888,7 @@
       <c r="P20" s="10">
         <v>0.70225</v>
       </c>
-      <c r="Q20" s="24">
+      <c r="Q20" s="26">
         <v>-2.78023</v>
       </c>
       <c r="R20" s="10">
@@ -4889,7 +4901,7 @@
       <c r="U20" s="10">
         <v>0.70225</v>
       </c>
-      <c r="V20" s="24">
+      <c r="V20" s="26">
         <v>-2.91246</v>
       </c>
       <c r="W20" s="10">
@@ -4902,7 +4914,7 @@
       <c r="Z20" s="10">
         <v>0.70225</v>
       </c>
-      <c r="AA20" s="24">
+      <c r="AA20" s="26">
         <v>-2.3641</v>
       </c>
       <c r="AB20" s="10">
@@ -4916,7 +4928,7 @@
       <c r="A21" s="10">
         <v>0.75206</v>
       </c>
-      <c r="B21" s="24">
+      <c r="B21" s="26">
         <v>-3.96795</v>
       </c>
       <c r="C21" s="10">
@@ -4929,7 +4941,7 @@
       <c r="F21" s="10">
         <v>0.75206</v>
       </c>
-      <c r="G21" s="24">
+      <c r="G21" s="26">
         <v>-4.49133</v>
       </c>
       <c r="H21" s="10">
@@ -4955,7 +4967,7 @@
       <c r="P21" s="10">
         <v>0.75206</v>
       </c>
-      <c r="Q21" s="24">
+      <c r="Q21" s="26">
         <v>-2.98003</v>
       </c>
       <c r="R21" s="10">
@@ -4968,7 +4980,7 @@
       <c r="U21" s="10">
         <v>0.75206</v>
       </c>
-      <c r="V21" s="24">
+      <c r="V21" s="26">
         <v>-3.13156</v>
       </c>
       <c r="W21" s="10">
@@ -4981,7 +4993,7 @@
       <c r="Z21" s="10">
         <v>0.75206</v>
       </c>
-      <c r="AA21" s="24">
+      <c r="AA21" s="26">
         <v>-2.54966</v>
       </c>
       <c r="AB21" s="10">
@@ -4995,7 +5007,7 @@
       <c r="A22" s="10">
         <v>0.80139</v>
       </c>
-      <c r="B22" s="24">
+      <c r="B22" s="26">
         <v>-4.12722</v>
       </c>
       <c r="C22" s="10">
@@ -5008,7 +5020,7 @@
       <c r="F22" s="10">
         <v>0.80139</v>
       </c>
-      <c r="G22" s="24">
+      <c r="G22" s="26">
         <v>-4.6816</v>
       </c>
       <c r="H22" s="10">
@@ -5034,7 +5046,7 @@
       <c r="P22" s="10">
         <v>0.80139</v>
       </c>
-      <c r="Q22" s="24">
+      <c r="Q22" s="26">
         <v>-3.10766</v>
       </c>
       <c r="R22" s="10">
@@ -5047,7 +5059,7 @@
       <c r="U22" s="10">
         <v>0.80139</v>
       </c>
-      <c r="V22" s="24">
+      <c r="V22" s="26">
         <v>-3.27233</v>
       </c>
       <c r="W22" s="10">
@@ -5060,7 +5072,7 @@
       <c r="Z22" s="10">
         <v>0.80139</v>
       </c>
-      <c r="AA22" s="24">
+      <c r="AA22" s="26">
         <v>-2.66837</v>
       </c>
       <c r="AB22" s="10">
@@ -5074,7 +5086,7 @@
       <c r="A23" s="10">
         <v>0.85108</v>
       </c>
-      <c r="B23" s="24">
+      <c r="B23" s="26">
         <v>-4.37868</v>
       </c>
       <c r="C23" s="10">
@@ -5087,7 +5099,7 @@
       <c r="F23" s="10">
         <v>0.85108</v>
       </c>
-      <c r="G23" s="24">
+      <c r="G23" s="26">
         <v>-4.98583</v>
       </c>
       <c r="H23" s="10">
@@ -5113,7 +5125,7 @@
       <c r="P23" s="10">
         <v>0.85108</v>
       </c>
-      <c r="Q23" s="24">
+      <c r="Q23" s="26">
         <v>-3.30865</v>
       </c>
       <c r="R23" s="10">
@@ -5126,7 +5138,7 @@
       <c r="U23" s="10">
         <v>0.85108</v>
       </c>
-      <c r="V23" s="24">
+      <c r="V23" s="26">
         <v>-3.49556</v>
       </c>
       <c r="W23" s="10">
@@ -5139,7 +5151,7 @@
       <c r="Z23" s="10">
         <v>0.85108</v>
       </c>
-      <c r="AA23" s="24">
+      <c r="AA23" s="26">
         <v>-2.85511</v>
       </c>
       <c r="AB23" s="10">
@@ -5153,7 +5165,7 @@
       <c r="A24" s="10">
         <v>0.90339</v>
       </c>
-      <c r="B24" s="24">
+      <c r="B24" s="26">
         <v>-4.53568</v>
       </c>
       <c r="C24" s="10">
@@ -5166,7 +5178,7 @@
       <c r="F24" s="10">
         <v>0.90339</v>
       </c>
-      <c r="G24" s="24">
+      <c r="G24" s="26">
         <v>-5.17875</v>
       </c>
       <c r="H24" s="10">
@@ -5192,7 +5204,7 @@
       <c r="P24" s="10">
         <v>0.90339</v>
       </c>
-      <c r="Q24" s="24">
+      <c r="Q24" s="26">
         <v>-3.43357</v>
       </c>
       <c r="R24" s="10">
@@ -5205,7 +5217,7 @@
       <c r="U24" s="10">
         <v>0.90339</v>
       </c>
-      <c r="V24" s="24">
+      <c r="V24" s="26">
         <v>-3.63537</v>
       </c>
       <c r="W24" s="10">
@@ -5218,7 +5230,7 @@
       <c r="Z24" s="10">
         <v>0.90339</v>
       </c>
-      <c r="AA24" s="24">
+      <c r="AA24" s="26">
         <v>-2.97111</v>
       </c>
       <c r="AB24" s="10">
@@ -5232,7 +5244,7 @@
       <c r="A25" s="10">
         <v>0.95085</v>
       </c>
-      <c r="B25" s="24">
+      <c r="B25" s="26">
         <v>-4.81705</v>
       </c>
       <c r="C25" s="10">
@@ -5245,7 +5257,7 @@
       <c r="F25" s="10">
         <v>0.95085</v>
       </c>
-      <c r="G25" s="24">
+      <c r="G25" s="26">
         <v>-5.52914</v>
       </c>
       <c r="H25" s="10">
@@ -5271,7 +5283,7 @@
       <c r="P25" s="10">
         <v>0.95085</v>
       </c>
-      <c r="Q25" s="24">
+      <c r="Q25" s="26">
         <v>-3.65669</v>
       </c>
       <c r="R25" s="10">
@@ -5284,7 +5296,7 @@
       <c r="U25" s="10">
         <v>0.95085</v>
       </c>
-      <c r="V25" s="24">
+      <c r="V25" s="26">
         <v>-3.88649</v>
       </c>
       <c r="W25" s="10">
@@ -5297,7 +5309,7 @@
       <c r="Z25" s="10">
         <v>0.95085</v>
       </c>
-      <c r="AA25" s="24">
+      <c r="AA25" s="26">
         <v>-3.17891</v>
       </c>
       <c r="AB25" s="10">
@@ -5311,7 +5323,7 @@
       <c r="A26" s="9">
         <v>1</v>
       </c>
-      <c r="B26" s="24">
+      <c r="B26" s="26">
         <v>-4.84767</v>
       </c>
       <c r="C26" s="10">
@@ -5324,7 +5336,7 @@
       <c r="F26" s="9">
         <v>1</v>
       </c>
-      <c r="G26" s="24">
+      <c r="G26" s="26">
         <v>-5.56764</v>
       </c>
       <c r="H26" s="10">
@@ -5350,7 +5362,7 @@
       <c r="P26" s="9">
         <v>1</v>
       </c>
-      <c r="Q26" s="24">
+      <c r="Q26" s="26">
         <v>-3.68095</v>
       </c>
       <c r="R26" s="10">
@@ -5363,7 +5375,7 @@
       <c r="U26" s="9">
         <v>1</v>
       </c>
-      <c r="V26" s="24">
+      <c r="V26" s="26">
         <v>-3.91392</v>
       </c>
       <c r="W26" s="10">
@@ -5376,7 +5388,7 @@
       <c r="Z26" s="9">
         <v>1</v>
       </c>
-      <c r="AA26" s="24">
+      <c r="AA26" s="26">
         <v>-3.20151</v>
       </c>
       <c r="AB26" s="10">
@@ -5557,7 +5569,7 @@
       <c r="X3" s="5"/>
       <c r="Y3" s="6"/>
       <c r="Z3" s="18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA3" s="19">
         <v>49903</v>
@@ -5567,7 +5579,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" s="10">
         <v>-6.65384</v>
@@ -5580,7 +5592,7 @@
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4" s="10">
         <v>6.11839</v>
@@ -5593,7 +5605,7 @@
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L4" s="5">
         <v>0.185553</v>
@@ -5606,7 +5618,7 @@
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q4" s="5">
         <v>-8.27627</v>
@@ -5619,7 +5631,7 @@
       </c>
       <c r="T4" s="6"/>
       <c r="U4" s="20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V4" s="5">
         <v>7.72579</v>
@@ -5632,7 +5644,7 @@
       </c>
       <c r="Y4" s="6"/>
       <c r="Z4" s="20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA4" s="22">
         <v>-0.0172085</v>
@@ -5649,7 +5661,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>7</v>
@@ -5662,7 +5674,7 @@
         <v>6</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>7</v>
@@ -5675,7 +5687,7 @@
         <v>6</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M5" s="8" t="s">
         <v>7</v>
@@ -5688,7 +5700,7 @@
         <v>6</v>
       </c>
       <c r="Q5" s="23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R5" s="8" t="s">
         <v>7</v>
@@ -5701,7 +5713,7 @@
         <v>6</v>
       </c>
       <c r="V5" s="23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W5" s="8" t="s">
         <v>7</v>
@@ -5714,7 +5726,7 @@
         <v>6</v>
       </c>
       <c r="AA5" s="23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB5" s="8" t="s">
         <v>7</v>
